--- a/plantillas/4.xlsx
+++ b/plantillas/4.xlsx
@@ -1,45 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$8</definedName>
-    <definedName name="MARCA_2">Listas!$E$2:$E$2</definedName>
-    <definedName name="MARCA_3">Listas!$F$2:$F$8</definedName>
-    <definedName name="MARCA_4">Listas!$G$2:$G$4</definedName>
-    <definedName name="MARCA_5">Listas!$H$2:$H$6</definedName>
-    <definedName name="MARCA_6">Listas!$I$2:$I$3</definedName>
-    <definedName name="MARCA_7">Listas!$J$2:$J$2</definedName>
-    <definedName name="MARCA_8">Listas!$K$2:$K$3</definedName>
-    <definedName name="MARCA_9">Listas!$L$2:$L$6</definedName>
-    <definedName name="MARCA_10">Listas!$M$2:$M$4</definedName>
-    <definedName name="MARCA_11">Listas!$N$2:$N$16</definedName>
-    <definedName name="MARCA_12">Listas!$O$2:$O$3</definedName>
-    <definedName name="MARCA_13">Listas!$P$2:$P$25</definedName>
-    <definedName name="MARCA_14">Listas!$Q$2:$Q$3</definedName>
-    <definedName name="MARCA_15">Listas!$R$2:$R$10</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$2</definedName>
-    <definedName name="MARCA_17">Listas!$T$2:$T$6</definedName>
+    <definedName name="MARCA_2">Listas!$E$2:$E$8</definedName>
+    <definedName name="MARCA_3">Listas!$F$2:$F$4</definedName>
+    <definedName name="MARCA_4">Listas!$G$2:$G$6</definedName>
+    <definedName name="MARCA_5">Listas!$H$2:$H$3</definedName>
+    <definedName name="MARCA_6">Listas!$I$2:$I$2</definedName>
+    <definedName name="MARCA_7">Listas!$J$2:$J$3</definedName>
+    <definedName name="MARCA_8">Listas!$K$2:$K$6</definedName>
+    <definedName name="MARCA_9">Listas!$L$2:$L$4</definedName>
+    <definedName name="MARCA_10">Listas!$M$2:$M$18</definedName>
+    <definedName name="MARCA_11">Listas!$N$2:$N$3</definedName>
+    <definedName name="MARCA_12">Listas!$O$2:$O$25</definedName>
+    <definedName name="MARCA_13">Listas!$P$2:$P$2</definedName>
+    <definedName name="MARCA_14">Listas!$Q$2:$Q$10</definedName>
+    <definedName name="MARCA_15">Listas!$R$2:$R$2</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$6</definedName>
+    <definedName name="MARCA_17">Listas!$T$2:$T$2</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$2</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$2</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$2</definedName>
-    <definedName name="MARCA_21">Listas!$X$2:$X$2</definedName>
-    <definedName name="MARCA_22">Listas!$Y$2:$Y$6</definedName>
-    <definedName name="MARCA_23">Listas!$Z$2:$Z$10</definedName>
+    <definedName name="MARCA_21">Listas!$X$2:$X$6</definedName>
+    <definedName name="MARCA_22">Listas!$Y$2:$Y$10</definedName>
+    <definedName name="MARCA_23">Listas!$Z$2:$Z$6</definedName>
     <definedName name="MARCA_24">Listas!$AA$2:$AA$6</definedName>
-    <definedName name="MARCA_25">Listas!$AB$2:$AB$6</definedName>
-    <definedName name="MARCA_26">Listas!$AC$2:$AC$7</definedName>
+    <definedName name="MARCA_25">Listas!$AB$2:$AB$7</definedName>
     <definedName name="MESES">Listas!$C$2:$C$5</definedName>
-    <definedName name="MARCAS">Listas!$A$2:$A$27</definedName>
+    <definedName name="MARCAS">Listas!$A$2:$A$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8285,7 +8284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8311,125 +8310,120 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ASCAN</t>
+          <t>BROWN'S</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>BROWN'S</t>
+          <t>ESBILAC</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>OLA</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PEDIGREE</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>PEDIGREE</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PURINA</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
-        <is>
-          <t>WHISKAS</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
         <is>
           <t>ZOO MED</t>
         </is>
@@ -8457,125 +8451,120 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ASCAN CACHORRO 2KG · 90409500000</t>
+          <t>BRW ENCORE CACATUA 2LB · 90739670000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BRW ENCORE CACATUA 2LB · 90739670000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
+          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
+          <t>OLA COBAYOS 800GRS. · 90405610000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>OLA COBAYOS 800GRS. · 90405610000</t>
+          <t>PEDIGREE LATA  CHOICE CUTS BEEF 375 · 90413790000</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>PEDIGREE LATA  CHOICE CUTS BEEF 375 · 90413790000</t>
+          <t>PF HUESO/ CARNAZA SABOR NATURA 5-6IN · 93514320000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR NATURA 5-6IN · 93514320000</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>UC SNACK BARRA RELLENA DE POLLO 1UD · 93513080000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>UC SNACK BARRA RELLENA DE POLLO 1UD · 93513080000</t>
+          <t>SUPER GATO 1.5KG · 93500000800</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>SUPER GATO 1.5KG · 93500000800</t>
+          <t>D SK ALIM LATA TOCINO/VEGETALES 400GR · 93511680000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA TOCINO/VEGETALES 400GR · 93511680000</t>
+          <t>D SUPRA ADULTO 10KG · 93508880000</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>D SUPRA ADULTO 10KG · 93508880000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>WHISKAS CARNE ORIGINAL 1.5KG · 90408360000</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
-        <is>
-          <t>WHISKAS CARNE ORIGINAL 1.5KG · 90408360000</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
         <is>
           <t>ZM ALIM TORTUGAS REPTISTICKS 141GR · 90415930000</t>
         </is>
@@ -8584,7 +8573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASCAN</t>
+          <t>BROWN'S</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8601,92 +8590,87 @@
           <t>AQ GRANULADO P PECES TROPICALES 3.25OZ · 93500000243</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BRW ENCORE CACATUA GOURMET 3LB · 90413120000</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BRW ENCORE CACATUA GOURMET 3LB · 90413120000</t>
+          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
           <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>KORDON VITAMINAS P CONEJO 2 OZ · 90720780000</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS P CONEJO 2 OZ · 90720780000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>NV TRANQUILIZANTES PERRO/GATO 1OZ · 90332560000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTES PERRO/GATO 1OZ · 90332560000</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>OLA PERIQUITOS AUST/ BUDGERIGARS 800G · 90405510000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
           <t>PEDIGREE LATA CACHORRO 375GR · 90408540000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>D SUPRA CACHORRO 10KG · 93508930000</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>D SUPRA CACHORRO 10KG · 93508930000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>WHISKAS GATITOS 1.4KG · 93515190000</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
-        <is>
-          <t>WHISKAS GATITOS 1.4KG · 93515190000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
         <is>
           <t>ZM ALIMENTO EN BLOQUE PARA PECES 1 · 93517470000</t>
         </is>
@@ -8695,7 +8679,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BROWN'S</t>
+          <t>ESBILAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8712,72 +8696,72 @@
           <t>AQ GRANULADO P PECES TROPICALES 6.5OZ · 93500000242</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BRW ENCORE CONEJO 2LB · 90739690000</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BRW ENCORE CONEJO 2LB · 90739690000</t>
+          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>PEDIGREE LATA CHOPPED BEEF 375GR · 90408530000</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>PRO PET 18KG ADULTO · 93500000600</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>TETRA ALIMENTO BETTA WORMS 0.98OZ · 93518650000</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>TETRA ALIMENTO BETTA WORMS 0.98OZ · 93518650000</t>
+          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
-        <is>
-          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
         <is>
           <t>ZM ALIMENTO EN BLOQUE PARA PECES 6 · 93517480000</t>
         </is>
@@ -8786,7 +8770,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8803,62 +8787,62 @@
           <t>AQ HOJUELAS P PECES TROPICALES 0.45OZ · 93500000240</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>BRW ENCORE HASMTER/GERBIL 2LB · 90739680000</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>PEDIGREE LATA CHOPPED CHICKEN 375GR · 90408560000</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
-        <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
         <is>
           <t>ZM ALIMENTO P/TORTUGA ACUAT 425G · 90410650000</t>
         </is>
@@ -8867,7 +8851,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8880,62 +8864,62 @@
           <t>AQ HOJUELAS P PECES TROPICALES 1.02OZ · 93500000241</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>BRW ENCORE LORO 4 LB · 90403890000</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>PEDIGREE POUCH POLLO ADULTO 100GR · 93509400000</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
-        <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
         <is>
           <t>ZM ALIMENTO TORTUGA ACUATICA  52G · 90410660000</t>
         </is>
@@ -8944,7 +8928,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8957,32 +8941,32 @@
           <t>AQ HOJUELAS P/ GOLDFISH 1.02OZ · 93500000247</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>BRW ENCORE PERICO 2LB · 90739660000</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>PEDIGREE POUCH POLLO CACHORRO 100GR · 93509410000</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
@@ -8991,7 +8975,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9004,27 +8988,27 @@
           <t>AQ HOJUELAS P/ GOLDFISH 2.29OZ · 93500000246</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>D BRW ENCORE CLASSIC COBAYO 4LB · 90413090000</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>PEDIGREE POUCH RES ADULTO 100GR · 93509420000</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
@@ -9033,7 +9017,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9041,22 +9025,22 @@
           <t>MARCA_8</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>PEDIGREE POUCH RES CACHORRO 100GR · 93509390000</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 30KG · 93508950000</t>
         </is>
@@ -9065,7 +9049,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9073,22 +9057,22 @@
           <t>MARCA_9</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>PEDIGREE RAZA PEQ POUCH RES 100GR · 93512290000</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
@@ -9097,7 +9081,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9105,12 +9089,12 @@
           <t>MARCA_10</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
@@ -9119,7 +9103,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9127,12 +9111,12 @@
           <t>MARCA_11</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
@@ -9141,7 +9125,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9149,12 +9133,12 @@
           <t>MARCA_12</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
@@ -9163,7 +9147,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>OLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9171,12 +9155,12 @@
           <t>MARCA_13</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
@@ -9185,7 +9169,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PEDIGREE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9193,12 +9177,12 @@
           <t>MARCA_14</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>NS CHOICE POLLO Y CEBADA 5OZ MUESTRA · 90034020000</t>
         </is>
@@ -9207,7 +9191,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PEDIGREE</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9215,12 +9199,12 @@
           <t>MARCA_15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>NS CHOICE R GDE POLLO Y CEBADA 5OZ MUEST · 90034060000</t>
         </is>
@@ -9229,7 +9213,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9237,7 +9221,12 @@
           <t>MARCA_16</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
@@ -9246,7 +9235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PURINA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9254,7 +9243,12 @@
           <t>MARCA_17</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
@@ -9263,7 +9257,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9271,7 +9265,7 @@
           <t>MARCA_18</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
@@ -9280,7 +9274,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9288,7 +9282,7 @@
           <t>MARCA_19</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
         </is>
@@ -9297,7 +9291,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9305,7 +9299,7 @@
           <t>MARCA_20</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
@@ -9314,7 +9308,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9322,7 +9316,7 @@
           <t>MARCA_21</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
@@ -9331,7 +9325,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9339,7 +9333,7 @@
           <t>MARCA_22</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
@@ -9348,7 +9342,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9356,7 +9350,7 @@
           <t>MARCA_23</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
         </is>
@@ -9365,7 +9359,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9373,7 +9367,7 @@
           <t>MARCA_24</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
@@ -9382,24 +9376,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WHISKAS</t>
+          <t>ZOO MED</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>MARCA_25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MARCA_26</t>
         </is>
       </c>
     </row>
@@ -9582,32 +9564,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASCAN CACHORRO 2KG · 90409500000</t>
+          <t>BRW ENCORE CACATUA 2LB · 90739670000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90409500000</t>
+          <t>90739670000</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ASCAN</t>
+          <t>BROWN'S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRW ENCORE CACATUA 2LB · 90739670000</t>
+          <t>BRW ENCORE CACATUA GOURMET 3LB · 90413120000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90739670000</t>
+          <t>90413120000</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -9622,16 +9604,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRW ENCORE CACATUA GOURMET 3LB · 90413120000</t>
+          <t>BRW ENCORE CONEJO 2LB · 90739690000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90413120000</t>
+          <t>90739690000</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9642,16 +9624,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRW ENCORE CONEJO 2LB · 90739690000</t>
+          <t>BRW ENCORE HASMTER/GERBIL 2LB · 90739680000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90739690000</t>
+          <t>90739680000</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9662,16 +9644,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRW ENCORE HASMTER/GERBIL 2LB · 90739680000</t>
+          <t>BRW ENCORE LORO 4 LB · 90403890000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90739680000</t>
+          <t>90403890000</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9682,12 +9664,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRW ENCORE LORO 4 LB · 90403890000</t>
+          <t>BRW ENCORE PERICO 2LB · 90739660000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90403890000</t>
+          <t>90739660000</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -9702,16 +9684,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRW ENCORE PERICO 2LB · 90739660000</t>
+          <t>D BRW ENCORE CLASSIC COBAYO 4LB · 90413090000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90739660000</t>
+          <t>90413090000</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9722,36 +9704,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D BRW ENCORE CLASSIC COBAYO 4LB · 90413090000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90413090000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BROWN'S</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90401410000</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9762,16 +9744,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
+          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90401410000</t>
+          <t>93519360000</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9782,36 +9764,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>93519360000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9822,16 +9804,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9842,16 +9824,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9862,16 +9844,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9882,36 +9864,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>93510440000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>93510440000</t>
+          <t>90480080000</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9922,32 +9904,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
+          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90480080000</t>
+          <t>90404930000</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
+          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90404930000</t>
+          <t>90720740000</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -9955,23 +9937,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
+          <t>KORDON VITAMINAS P CONEJO 2 OZ · 90720780000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90720740000</t>
+          <t>90720780000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9982,36 +9964,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS P CONEJO 2 OZ · 90720780000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90720780000</t>
+          <t>90409680000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10022,16 +10004,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10042,16 +10024,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90400340000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10062,16 +10044,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90400340000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10082,36 +10064,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93513280000</t>
+          <t>90322660000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90322660000</t>
+          <t>90322650000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10122,16 +10104,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90322650000</t>
+          <t>90301720000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10142,36 +10124,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90301720000</t>
+          <t>93510820000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93510820000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10182,16 +10164,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10202,16 +10184,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93505950000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -10251,7 +10233,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10271,7 +10253,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10291,7 +10273,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10362,12 +10344,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>90410820000</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -10382,16 +10364,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90415960000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10402,16 +10384,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90410810000</t>
+          <t>90415960000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -10422,12 +10404,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>90410810000</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -10442,16 +10424,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10462,36 +10444,36 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90328330000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTES PERRO/GATO 1OZ · 90332560000</t>
+          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90332560000</t>
+          <t>90328330000</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -10502,32 +10484,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
+          <t>NV TRANQUILIZANTES PERRO/GATO 1OZ · 90332560000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93500000429</t>
+          <t>90332560000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93500000461</t>
+          <t>93500000429</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -10542,16 +10524,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>93500000461</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10562,16 +10544,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90034110000</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10582,16 +10564,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034110000</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10602,16 +10584,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90033980000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10622,12 +10604,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90034200000</t>
+          <t>90033980000</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -10642,12 +10624,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
+          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90034180000</t>
+          <t>90034200000</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -10662,12 +10644,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
+          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90034290000</t>
+          <t>90034180000</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -10682,12 +10664,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
+          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90034190000</t>
+          <t>90034290000</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -10702,16 +10684,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90034190000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10722,12 +10704,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -10742,16 +10724,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -10762,16 +10744,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5OZ MUESTRA · 90034020000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>90034020000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10782,12 +10764,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NS CHOICE R GDE POLLO Y CEBADA 5OZ MUEST · 90034060000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5OZ MUESTRA · 90034020000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>90034060000</t>
+          <t>90034020000</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -10802,16 +10784,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE R GDE POLLO Y CEBADA 5OZ MUEST · 90034060000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90034060000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10822,12 +10804,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -10842,12 +10824,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -10862,16 +10844,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>93500000479</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10882,16 +10864,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>93500000471</t>
+          <t>93500000479</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10902,16 +10884,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>93500000422</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10922,12 +10904,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>93500000435</t>
+          <t>93500000422</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -10942,12 +10924,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>93500000445</t>
+          <t>93500000435</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -10962,16 +10944,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000445</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10982,36 +10964,36 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OLA COBAYOS 800GRS. · 90405610000</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>90405610000</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OLA PERIQUITOS AUST/ BUDGERIGARS 800G · 90405510000</t>
+          <t>OLA COBAYOS 800GRS. · 90405610000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>90405510000</t>
+          <t>90405610000</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11051,7 +11033,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11271,7 +11253,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11291,7 +11273,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11351,7 +11333,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11431,7 +11413,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11471,7 +11453,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11551,7 +11533,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11631,7 +11613,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11771,7 +11753,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12029,7 +12011,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/4.xlsx
+++ b/plantillas/4.xlsx
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/4.xlsx
+++ b/plantillas/4.xlsx
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
